--- a/data/credit_bond_all_2026-10-29.xlsx
+++ b/data/credit_bond_all_2026-10-29.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6100/1.5850</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -1891,7 +1891,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X8" s="3"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -2075,7 +2079,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7300/1.6800</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -2111,7 +2115,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X9" s="3"/>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>1.85%~1.95%</t>
+        </is>
+      </c>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
@@ -2236,60 +2244,68 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26浦发银行债02</t>
+          <t>26新兴际华MTN004</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>10-29 16:30</t>
-        </is>
-      </c>
-      <c r="C10" s="3"/>
+          <t>10-29 18:00</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>102684338.IB</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>50.0</v>
+        <v>7.0</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>1.47 ~ 1.87</t>
+        </is>
+      </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26浦发银行债01</t>
+          <t>26新兴际华MTN003</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>2.98Y+N</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.4824</t>
+          <t>1.6504</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6650/1.6300</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司</t>
+          <t>新兴际华集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>A+ 84.30</t>
+          <t>B- 39.72</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2299,7 +2315,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>10-29 09:30</t>
+          <t>10-29 09:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -2316,10 +2332,14 @@
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X10" s="3"/>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2328,24 +2348,28 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC10" s="3"/>
+          <t>本期中期票据发行金额为7亿元，募集资金拟用于偿还存量有息债务或补充日常流动资金周转。</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>中国农业银行股份有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
@@ -2355,7 +2379,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司2026年第二期金融债券</t>
+          <t>新兴际华集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2371,54 +2395,54 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>工业金属</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM10" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="AO10" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AQ10" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR10" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS10" s="3" t="inlineStr">
-        <is>
-          <t>股份制银行</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2426,12 +2450,12 @@
       </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX10" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY10" s="3" t="inlineStr">
@@ -2444,7 +2468,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26新兴际华MTN004</t>
+          <t>26宁河西MTN003</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2452,56 +2476,60 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>102684354.IB</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.47 ~ 1.87</t>
+          <t>1.43 ~ 1.83</t>
         </is>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26新兴际华MTN003</t>
+          <t>24宁河西MTN004B</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2.98Y+N</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.6504</t>
+          <t>1.5958</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>1.6650/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>新兴际华集团有限公司</t>
+          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>B- 39.72</t>
+          <t>C+ 30.62</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2528,10 +2556,14 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X11" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>1.54%~1.64%</t>
+        </is>
+      </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2540,17 +2572,17 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为7亿元，募集资金拟用于偿还存量有息债务或补充日常流动资金周转。</t>
+          <t>发行人本期发行15亿元中期票据将全部用于偿还发行人债务融资工具本金[26宁河西SCP001,26宁河西SCP002,26宁河西SCP003]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中国银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
@@ -2561,7 +2593,7 @@
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
@@ -2571,7 +2603,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>新兴际华集团有限公司2026年度第四期中期票据</t>
+          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2607,27 +2639,27 @@
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>工业金属</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2642,12 +2674,12 @@
       </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX11" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY11" s="3" t="inlineStr">
@@ -2655,12 +2687,14 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ11" s="3"/>
+      <c r="AZ11" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26宁河西MTN003</t>
+          <t>26物流股份MTN001</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2668,19 +2702,23 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>102684340.IB</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.43 ~ 1.83</t>
+          <t>1.49 ~ 1.69</t>
         </is>
       </c>
       <c r="H12" s="3"/>
@@ -2692,17 +2730,17 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>24宁河西MTN004B</t>
+          <t>26物流股份SCP002</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>148D</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.5958</t>
+          <t>1.4990</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2712,12 +2750,12 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司</t>
+          <t>中国物流股份有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.62</t>
+          <t>D 5.00</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2727,7 +2765,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>10-29 09:00</t>
+          <t>10-29 11:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2744,29 +2782,33 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X12" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>1.65%~1.75%</t>
+        </is>
+      </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行15亿元中期票据将全部用于偿还发行人债务融资工具本金[26宁河西SCP001,26宁河西SCP002,26宁河西SCP003]</t>
+          <t>本期中期票据发行规模为不超过5亿元,拟全部用于偿还公司有息债务</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
@@ -2777,7 +2819,7 @@
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG12" s="3" t="inlineStr">
@@ -2787,7 +2829,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司2026年度第三期中期票据</t>
+          <t>中国物流股份有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2823,27 +2865,27 @@
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>物流</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>物流</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>物流</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -2871,14 +2913,12 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ12" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ12" s="3"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26物流股份MTN001</t>
+          <t>26华新建材MTN001</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2886,41 +2926,47 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>102690095.IB</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F13" s="3"/>
+        <v>12.0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>12.0</v>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.49 ~ 1.69</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26物流股份SCP002</t>
+          <t>25华新K1</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>148D</t>
+          <t>3.21Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.4990</t>
+          <t>1.6387</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -2930,12 +2976,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>中国物流股份有限公司</t>
+          <t>华新建材集团股份有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>D 5.00</t>
+          <t>B- 46.25</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2945,7 +2991,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>10-29 11:00</t>
+          <t>10-29 14:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -2962,29 +3008,33 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X13" s="3"/>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>1.58%~1.68%</t>
+        </is>
+      </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖北省-黄石市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模为不超过5亿元,拟全部用于偿还公司有息债务</t>
+          <t>发行人本期中期票据发行金额为12亿元,募集资金扣除发行费用后,拟将不超过3.30亿元用于偿还发行人银行贷款、银行承兑汇票等有息债务,剩余部分用于补充流动资金。</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>中信证券股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
@@ -2995,7 +3045,7 @@
       </c>
       <c r="AF13" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>外商独资企业</t>
         </is>
       </c>
       <c r="AG13" s="3" t="inlineStr">
@@ -3005,7 +3055,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>中国物流股份有限公司2026年度第一期中期票据</t>
+          <t>华新建材集团股份有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3041,27 +3091,27 @@
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>物流</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>物流</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>物流</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3094,7 +3144,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26华新水泥MTN001</t>
+          <t>26华光环保MTN013</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3102,41 +3152,45 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>102684349.IB</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1+1</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>25华新K1</t>
+          <t>25华光环保MTN003(科创债)</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>3.21Y</t>
+          <t>295D</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.6387</t>
+          <t>1.4970</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -3146,12 +3200,12 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>华新建材集团股份有限公司</t>
+          <t>无锡华光环保能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 46.25</t>
+          <t>C- 22.31</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3161,7 +3215,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>10-29 14:00</t>
+          <t>10-29 09:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3178,10 +3232,14 @@
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X14" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>1.48%~1.52%</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3190,17 +3248,17 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>湖北省-黄石市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为12亿元,募集资金扣除发行费用后,拟将不超过3.30亿元用于偿还发行人银行贷款、银行承兑汇票等有息债务,剩余部分用于补充流动资金。</t>
+          <t>本期中期票据拟发行1.00亿元，用于偿还发行人有息负债[26华光环保SCP010]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,兴业银行股份有限公司</t>
+          <t>招商银行股份有限公司,中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3211,7 +3269,7 @@
       </c>
       <c r="AF14" s="3" t="inlineStr">
         <is>
-          <t>外商独资企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG14" s="3" t="inlineStr">
@@ -3221,7 +3279,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>华新建材集团股份有限公司2026年度第一期中期票据</t>
+          <t>无锡华光环保能源集团股份有限公司2026年度第十三期中期票据</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3231,7 +3289,7 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2029-10-30</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
@@ -3257,32 +3315,32 @@
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>电力设备制造</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>专用设备</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-10-30</t>
         </is>
       </c>
       <c r="AV14" s="3" t="inlineStr">
@@ -3292,7 +3350,7 @@
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr">
@@ -3310,7 +3368,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26华光环保MTN013</t>
+          <t>26闽投SCP003</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3318,41 +3376,45 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>012682568.IB</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1+1</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.20 ~ 1.50</t>
         </is>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>25华光环保MTN003(科创债)</t>
+          <t>26闽投SCP002</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>295D</t>
+          <t>204D</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.4970</t>
+          <t>1.4399</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -3362,12 +3424,12 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>无锡华光环保能源集团股份有限公司</t>
+          <t>福建省投资开发集团有限责任公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 22.31</t>
+          <t>C- 23.32</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3377,7 +3439,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>10-29 09:00</t>
+          <t>10-29 10:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3394,10 +3456,14 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X15" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>1.39%~1.43%</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3406,23 +3472,23 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟发行1.00亿元，用于偿还发行人有息负债[26华光环保SCP010]</t>
+          <t>发行人本次发行规模为人民币10.00亿元，均用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国农业银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3437,7 +3503,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>无锡华光环保能源集团股份有限公司2026年度第十三期中期票据</t>
+          <t>福建省投资开发集团有限责任公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3447,7 +3513,7 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2028-10-30</t>
+          <t>2027-04-28</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
@@ -3473,32 +3539,32 @@
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>电力设备制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>专用设备</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
         <is>
-          <t>2027-10-30</t>
+          <t/>
         </is>
       </c>
       <c r="AV15" s="3" t="inlineStr">
@@ -3508,7 +3574,7 @@
       </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr">
@@ -3526,7 +3592,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26闽投SCP003</t>
+          <t>26浦发集团MTN001</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3534,56 +3600,60 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>102684337.IB</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.50</t>
+          <t>1.36 ~ 1.66</t>
         </is>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26闽投SCP002</t>
+          <t>19浦集03</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>204D</t>
+          <t>3.08Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.4399</t>
+          <t>1.5541</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6100/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>福建省投资开发集团有限责任公司</t>
+          <t>上海浦东发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 23.32</t>
+          <t>C- 24.19</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3593,7 +3663,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>10-29 10:00</t>
+          <t>10-29 09:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3613,7 +3683,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X16" s="3"/>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>1.53%~1.63%</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3622,23 +3696,23 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>上海市-浦东新区</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行规模为人民币10.00亿元，均用于偿还发行人有息债务。</t>
+          <t>本期中期票据拟用于偿还25浦发集团SCP006和25浦发集团SCP007兑付的过桥银行贷款[25浦发集团SCP006,25浦发集团SCP007]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国农业银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,上海银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3653,7 +3727,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>福建省投资开发集团有限责任公司2026年度第三期超短期融资券</t>
+          <t>上海浦东发展(集团)有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3663,7 +3737,7 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2027-04-28</t>
+          <t>2029-10-30</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
@@ -3684,12 +3758,12 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
@@ -3699,17 +3773,17 @@
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3742,7 +3816,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26浦发集团MTN001</t>
+          <t>26闽高速SCP003</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3750,56 +3824,60 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>012682565.IB</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>40.0</v>
+        <v>6.0</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.36 ~ 1.66</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>19浦集03</t>
+          <t>26闽高速SCP002</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>3.08Y</t>
+          <t>264D</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.5541</t>
+          <t>1.4640</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4600/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展(集团)有限公司</t>
+          <t>福建省高速公路集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 24.19</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3829,7 +3907,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X17" s="3"/>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>1.43%~1.47%</t>
+        </is>
+      </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3838,23 +3920,23 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>上海市-浦东新区</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟用于偿还25浦发集团SCP006和25浦发集团SCP007兑付的过桥银行贷款[25浦发集团SCP006,25浦发集团SCP007]</t>
+          <t>发行人本期超短期融资券发行规模为人民币6亿元，用于偿还发行人到期债务</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,上海银行股份有限公司,兴业银行股份有限公司</t>
+          <t>交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -3869,7 +3951,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展(集团)有限公司2026年度第一期中期票据</t>
+          <t>福建省高速公路集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -3879,7 +3961,7 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2029-10-30</t>
+          <t>2027-07-27</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
@@ -3900,32 +3982,32 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -3958,64 +4040,68 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26闽高速SCP003</t>
+          <t>26湖产04</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>10-29 18:00</t>
-        </is>
-      </c>
-      <c r="C18" s="3"/>
+          <t>10-29 17:00</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>284398.SH</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.60 ~ 2.30</t>
         </is>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26闽高速SCP002</t>
+          <t>26湖州产投PPN002</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>264D</t>
+          <t>2.98Y+2.00Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.4640</t>
+          <t>1.7302</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1.4500/--</t>
+          <t>1.7400/1.6400</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>福建省高速公路集团有限公司</t>
+          <t>湖州市产业投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C- 24.26</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4025,7 +4111,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>10-29 09:00</t>
+          <t>10-29 15:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4035,17 +4121,21 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X18" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4054,23 +4144,23 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券发行规模为人民币6亿元，用于偿还发行人到期债务</t>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还回售或到期的公司债券本金或置换偿还公司债券本金的自有资金[23湖产V1,25湖产D2]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>交通银行股份有限公司</t>
+          <t>浙商证券股份有限公司,五矿证券有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4080,73 +4170,77 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>福建省高速公路集团有限公司2026年度第三期超短期融资券</t>
+          <t>湖州市产业投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2027-07-27</t>
-        </is>
-      </c>
-      <c r="AK18" s="3"/>
+          <t>2031-11-02</t>
+        </is>
+      </c>
+      <c r="AK18" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL18" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="AM18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-11-02</t>
         </is>
       </c>
       <c r="AV18" s="3" t="inlineStr">
@@ -4156,7 +4250,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4174,53 +4268,53 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26湖产04</t>
+          <t>26广西林业SCP004</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>10-29 17:00</t>
+          <t>10-29 18:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>284398.SH</t>
+          <t>012682571.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>9.0</v>
+        <v>2.5</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.30</t>
+          <t>1.70 ~ 2.10</t>
         </is>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26湖州产投PPN002</t>
+          <t>26广西林业SCP003</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.98Y+2.00Y</t>
+          <t>257D</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.7302</t>
+          <t>1.8315</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4230,12 +4324,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>湖州市产业投资发展集团有限公司</t>
+          <t>广西林业集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 24.26</t>
+          <t>C- 13.19</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4245,7 +4339,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>10-29 15:00</t>
+          <t>10-29 09:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4255,42 +4349,46 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X19" s="3"/>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>1.76%~1.80%</t>
+        </is>
+      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,全部用于偿还回售或到期的公司债券本金或置换偿还公司债券本金的自有资金[23湖产V1,25湖产D2]</t>
+          <t>本期超短期融资券基础发行规模0亿元，发行金额上限2.5亿元，募集资金全部用于偿还发行人本部及合并报表范围子公司有息债务。</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司,五矿证券有限公司</t>
+          <t>中国光大银行股份有限公司,广西北部湾银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4300,79 +4398,75 @@
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>湖州市产业投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>广西林业集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2031-11-02</t>
-        </is>
-      </c>
-      <c r="AK19" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-07-27</t>
+        </is>
+      </c>
+      <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>林业</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>林木种植</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>林业</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM19" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="AO19" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ19" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR19" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS19" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
-        <is>
-          <t>2029-11-02</t>
-        </is>
-      </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4380,7 +4474,7 @@
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX19" s="3" t="inlineStr">
@@ -4398,7 +4492,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26广西林业SCP004</t>
+          <t>26绿城地产MTN006</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4406,56 +4500,60 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C20" s="3"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>102690099.IB</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.5</v>
+        <v>10.0</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.10</t>
+          <t>3.00 ~ 3.35</t>
         </is>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26广西林业SCP003</t>
+          <t>26绿城地产MTN005</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>257D</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.8315</t>
+          <t>3.2931</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/3.2900</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>广西林业集团有限公司</t>
+          <t>绿城房地产集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C- 13.19</t>
+          <t>C+ 31.58</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4482,40 +4580,44 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X20" s="3"/>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>3.56%~3.66%</t>
+        </is>
+      </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行规模0亿元，发行金额上限2.5亿元，募集资金全部用于偿还发行人本部及合并报表范围子公司有息债务。</t>
+          <t>本期中期票据基础发行规模为0亿元,发行金额上限为10亿元,其中不超过4.4875亿元拟用于置换偿还到期债务融资工具本息的自有资金,不超过5.5125亿元用于偿还债务融资工具本息[23绿城房产MTN001(绿色),24绿城房产MTN005,25绿城地产MTN007,23绿城房产GN002]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,广西北部湾银行股份有限公司</t>
+          <t>中信证券股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr">
@@ -4525,7 +4627,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>广西林业集团有限公司2026年度第四期超短期融资券</t>
+          <t>绿城房地产集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4535,7 +4637,7 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2027-07-27</t>
+          <t>2029-10-30</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
@@ -4561,27 +4663,27 @@
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>林业</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>林木种植</t>
+          <t>住宅楼房</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>林业</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4609,12 +4711,14 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ20" s="3"/>
+      <c r="AZ20" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26绿城地产MTN006</t>
+          <t>26华电新能MTN003</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4622,56 +4726,60 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>102684357.IB</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>20Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>3.00 ~ 3.35</t>
+          <t>2.00 ~ 2.50</t>
         </is>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26绿城地产MTN005</t>
+          <t>24华新02</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>7.71Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>3.2931</t>
+          <t>1.8043</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8300/1.7800</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>绿城房地产集团有限公司</t>
+          <t>华电新能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.58</t>
+          <t>B- 49.07</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4691,36 +4799,44 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X21" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>2.12%~2.22%</t>
+        </is>
+      </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z21" s="3"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0亿元,发行金额上限为10亿元,其中不超过4.4875亿元拟用于置换偿还到期债务融资工具本息的自有资金,不超过5.5125亿元用于偿还债务融资工具本息[23绿城房产MTN001(绿色),24绿城房产MTN005,25绿城地产MTN007,23绿城房产GN002]</t>
+          <t>本期发行金额为20亿元,募集资金拟全部用于偿还发行人及发行人所属公司到期债务及补充流动资金。</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,北京银行股份有限公司</t>
+          <t>招商银行股份有限公司,兴业银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
@@ -4741,7 +4857,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>绿城房地产集团有限公司2026年度第六期中期票据</t>
+          <t>华电新能源集团股份有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4751,25 +4867,25 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2029-10-30</t>
+          <t>2046-11-02</t>
         </is>
       </c>
       <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="AM21" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -4777,27 +4893,27 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>住宅楼房</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -4830,7 +4946,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26华电新能MTN003</t>
+          <t>26湘高速SCP003</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4838,56 +4954,60 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>012682567.IB</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>20Y</t>
+          <t>0.71Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.50</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>24华新02</t>
+          <t>25湘高速MTN017</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>7.71Y</t>
+          <t>283D</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.8043</t>
+          <t>1.4720</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4900/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>华电新能源集团股份有限公司</t>
+          <t>湖南省高速公路集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 49.07</t>
+          <t>B- 37.83</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -4907,51 +5027,51 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X22" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>1.46%~1.50%</t>
+        </is>
+      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>湖南省</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为20亿元,募集资金拟全部用于偿还发行人及发行人所属公司到期债务及补充流动资金。</t>
+          <t>本期债务融资工具发行金额不超过15亿元,募集资金全部用于偿还公司到期债务。</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,兴业银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
@@ -4961,7 +5081,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>华电新能源集团股份有限公司2026年度第三期中期票据</t>
+          <t>湖南省高速公路集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -4971,13 +5091,17 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2046-11-02</t>
-        </is>
-      </c>
-      <c r="AK22" s="3"/>
+          <t>2027-07-17</t>
+        </is>
+      </c>
+      <c r="AK22" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL22" s="3" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="AM22" s="3" t="inlineStr">
@@ -4987,37 +5111,37 @@
       </c>
       <c r="AN22" s="3" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5050,7 +5174,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26湘高速SCP003</t>
+          <t>26锡产业SCP017</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5058,56 +5182,60 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C23" s="3"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>012682570.IB</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>0.71Y</t>
+          <t>0.38Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>15.0</v>
+        <v>4.0</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.30 ~ 1.45</t>
         </is>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>25湘高速MTN017</t>
+          <t>26锡产业SCP013</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>283D</t>
+          <t>145D</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.4720</t>
+          <t>1.4392</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5200/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>湖南省高速公路集团有限公司</t>
+          <t>无锡产业发展集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>B- 37.83</t>
+          <t>C- 21.71</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5134,10 +5262,14 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X23" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>1.41%~1.45%</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5146,17 +5278,17 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>湖南省</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额不超过15亿元,募集资金全部用于偿还公司到期债务。</t>
+          <t>本期超短期融资券发行金额4亿元用于归还发行人本部有息债务[26锡产业SCP009,26锡产业SCP005]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,浙商银行股份有限公司</t>
+          <t>宁波银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5177,7 +5309,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>湖南省高速公路集团有限公司2026年度第三期超短期融资券</t>
+          <t>无锡产业发展集团有限公司2026年度第十七期超短期融资券</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5187,14 +5319,10 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2027-07-17</t>
-        </is>
-      </c>
-      <c r="AK23" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-03-19</t>
+        </is>
+      </c>
+      <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
           <t>2026-11-02</t>
@@ -5212,32 +5340,32 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5270,7 +5398,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26锡产业SCP017</t>
+          <t>26龙盛MTN010(科创债)</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5278,56 +5406,60 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C24" s="3"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>102684344.IB</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>0.38Y</t>
+          <t>1.01Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.45</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26锡产业SCP013</t>
+          <t>26龙盛MTN009(科创债)</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>145D</t>
+          <t>362D</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.4392</t>
+          <t>1.5097</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/1.5100</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司</t>
+          <t>浙江龙盛集团股份有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C- 21.71</t>
+          <t>B- 49.73</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5354,10 +5486,14 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X24" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>1.44%~1.54%</t>
+        </is>
+      </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5366,28 +5502,28 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4亿元用于归还发行人本部有息债务[26锡产业SCP009,26锡产业SCP005]</t>
+          <t>本期债务融资工具发行规模为15亿元,拟用于偿还发行人即将到期的债务[26龙盛SCP003(科创债)]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,华夏银行股份有限公司</t>
+          <t>浙商银行股份有限公司,中国民生银行股份有限公司,中国光大银行股份有限公司,上海浦东发展银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -5397,7 +5533,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>无锡产业发展集团有限公司2026年度第十七期超短期融资券</t>
+          <t>浙江龙盛集团股份有限公司2026年度第十期科技创新债券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5407,7 +5543,7 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2027-03-19</t>
+          <t>2027-11-04</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
@@ -5433,27 +5569,27 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5486,7 +5622,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26龙盛MTN010(科创债)</t>
+          <t>26大渡河SCP001</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5494,56 +5630,60 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C25" s="3"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>012682566.IB</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>1.01Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.20 ~ 1.60</t>
         </is>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26龙盛MTN009(科创债)</t>
+          <t>GK25DDH1</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>362D</t>
+          <t>1.75Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.5097</t>
+          <t>1.4553</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.5100/--</t>
+          <t>1.4700/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>浙江龙盛集团股份有限公司</t>
+          <t>国能大渡河流域水电开发有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>B- 49.73</t>
+          <t>D+ 10.00</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5570,10 +5710,14 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="X25" s="3"/>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>1.40%~1.44%</t>
+        </is>
+      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5582,28 +5726,24 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
-        </is>
-      </c>
-      <c r="AB25" s="3" t="inlineStr">
-        <is>
-          <t>本期债务融资工具发行规模为15亿元,拟用于偿还发行人即将到期的债务[26龙盛SCP003(科创债)]</t>
-        </is>
-      </c>
+          <t>四川省-成都市</t>
+        </is>
+      </c>
+      <c r="AB25" s="3"/>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国民生银行股份有限公司,中国光大银行股份有限公司,上海浦东发展银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
@@ -5613,7 +5753,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>浙江龙盛集团股份有限公司2026年度第十期科技创新债券</t>
+          <t>国能大渡河流域水电开发有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5623,7 +5763,7 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2027-11-04</t>
+          <t>2027-07-27</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
@@ -5649,27 +5789,27 @@
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>水电</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -5702,7 +5842,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26大渡河SCP001</t>
+          <t>26津融资产MTN003</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5710,56 +5850,60 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C26" s="3"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>102684348.IB</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>10.0</v>
+        <v>2.5</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.60</t>
+          <t>1.90 ~ 2.40</t>
         </is>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>GK25DDH1</t>
+          <t>26津融资产MTN001</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>1.75Y</t>
+          <t>2.24Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.4553</t>
+          <t>2.0141</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0800/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>国能大渡河流域水电开发有限公司</t>
+          <t>天津津融资产管理有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>C- 13.16</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -5786,36 +5930,44 @@
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X26" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>2.32%~2.42%</t>
+        </is>
+      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
-        </is>
-      </c>
-      <c r="AB26" s="3"/>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>本期债券基础发行规模0亿元,发行金额上限2.50亿元,募集资金用于偿还发行人债务融资工具。[24津融资产PPN002]</t>
+        </is>
+      </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
@@ -5825,7 +5977,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>国能大渡河流域水电开发有限公司2026年度第一期超短期融资券</t>
+          <t>天津津融资产管理有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -5835,7 +5987,7 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2027-07-27</t>
+          <t>2029-10-30</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
@@ -5856,32 +6008,32 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>水电</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -5909,12 +6061,14 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ26" s="3"/>
+      <c r="AZ26" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26津融资产MTN003</t>
+          <t>26国证G2</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -5922,56 +6076,60 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>246351.SH</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.5</v>
+        <v>30.0</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.40</t>
+          <t>1.15 ~ 2.15</t>
         </is>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26津融资产MTN001</t>
+          <t>24国证G2</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2.24Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>2.0141</t>
+          <t>1.5661</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5600/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>天津津融资产管理有限公司</t>
+          <t>国开证券股份有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 13.16</t>
+          <t>B- 38.83</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -5981,7 +6139,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>10-29 09:00</t>
+          <t>10-29 15:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -5991,57 +6149,65 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X27" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.60%</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z27" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券基础发行规模0亿元,发行金额上限2.50亿元,募集资金用于偿还发行人债务融资工具。[24津融资产PPN002]</t>
+          <t>本期公司债券募集资金扣除发行费用后，拟用于补充公司流动资金。</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,渤海银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>天津津融资产管理有限公司2026年度第三期中期票据</t>
+          <t>国开证券股份有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6051,25 +6217,25 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2029-10-30</t>
+          <t>2029-11-02</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="AM27" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>金融</t>
@@ -6077,7 +6243,7 @@
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
@@ -6087,17 +6253,17 @@
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6130,7 +6296,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26国证G2</t>
+          <t>26金城03</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6140,7 +6306,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>246351.SH</t>
+          <t>284404.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -6149,34 +6315,34 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>30.0</v>
+        <v>4.7</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.15 ~ 2.15</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>24国证G2</t>
+          <t>26金城02</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.5661</t>
+          <t>1.6201</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6186,12 +6352,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>国开证券股份有限公司</t>
+          <t>张家港市金城投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B- 38.83</t>
+          <t>D+ 9.06</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6218,44 +6384,44 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X28" s="3"/>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后，拟用于补充公司流动资金。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金[23金城05]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>东吴证券股份有限公司,国金证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
@@ -6265,12 +6431,12 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>国开证券股份有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>张家港市金城投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
@@ -6296,32 +6462,32 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6354,7 +6520,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26金城03</t>
+          <t>26新师01</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6364,43 +6530,43 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>284404.SH</t>
+          <t>284209.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.7</v>
+        <v>5.0</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26金城02</t>
+          <t>25新师02</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>3.66Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.6201</t>
+          <t>1.8564</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6410,12 +6576,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>张家港市金城投资发展集团有限公司</t>
+          <t>新疆生产建设兵团第十二师国有投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.06</t>
+          <t>C- 16.83</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6425,7 +6591,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>10-29 15:00</t>
+          <t>10-29 16:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6442,10 +6608,14 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X29" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>2.00%~2.10%</t>
+        </is>
+      </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -6454,17 +6624,17 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>新疆维吾尔自治区-乌鲁木齐市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金[23金城05]</t>
+          <t>本期公司债券募集资金拟全部用于偿还到期债务[24天恒基MTN003]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,国金证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中信证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6485,7 +6655,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>张家港市金城投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>新疆生产建设兵团第十二师国有投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6495,10 +6665,14 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2029-11-02</t>
-        </is>
-      </c>
-      <c r="AK29" s="3"/>
+          <t>2031-11-02</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL29" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6516,12 +6690,12 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
@@ -6531,17 +6705,17 @@
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6574,7 +6748,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26新师01</t>
+          <t>26振兴K2</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6584,43 +6758,43 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>284209.SH</t>
+          <t>246339.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>25新师02</t>
+          <t>26川振兴K1</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>3.66Y</t>
+          <t>2.63Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.8564</t>
+          <t>1.6154</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -6630,12 +6804,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>新疆生产建设兵团第十二师国有投资发展集团有限公司</t>
+          <t>四川产业振兴基金投资集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 16.83</t>
+          <t>D+ 7.95</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6655,36 +6829,40 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X30" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>1.62%~1.72%</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区-乌鲁木齐市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金拟全部用于偿还到期债务[24天恒基MTN003]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还有息负债及置换发行人基金前期出资。[23四川振兴MTN002(科创票据)]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,申万宏源证券有限公司</t>
+          <t>申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -6705,24 +6883,20 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>新疆生产建设兵团第十二师国有投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>四川产业振兴基金投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-11-02</t>
-        </is>
-      </c>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-30</t>
+        </is>
+      </c>
+      <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6735,37 +6909,33 @@
       </c>
       <c r="AN30" s="3" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP30" s="3"/>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -6798,7 +6968,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26云产GTY1</t>
+          <t>26中金16</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6808,58 +6978,58 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>520560.SZ</t>
+          <t>246301.SH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+3</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.15 ~ 2.05</t>
         </is>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>23云产01</t>
+          <t>21中金G8</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>52D</t>
+          <t>5.11Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.4346</t>
+          <t>1.6049</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6100/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>广州白云产业投资集团有限公司</t>
+          <t>中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>B- 36.62</t>
+          <t>B- 44.41</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -6886,60 +7056,64 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X31" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>1.59%~1.69%</t>
+        </is>
+      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后，拟全部用于偿还有息债务</t>
+          <t>本期债券发行金额为不超过人民币60亿元(含60亿元),本期债券募集资金扣除发行费用后,拟全部用于补充流动资金,未来可能调整部分流动资金用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司</t>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>广州白云产业投资集团有限公司2026年面向专业投资者非公开发行可续期低碳转型挂钩公司债券(第一期)</t>
+          <t>中国国际金融股份有限公司2026年面向专业投资者公开发行公司债券(第八期)(品种二)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-11-02</t>
+          <t>2034-11-02</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
@@ -6960,37 +7134,37 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-11-02</t>
         </is>
       </c>
       <c r="AV31" s="3" t="inlineStr">
@@ -7000,7 +7174,7 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7018,7 +7192,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26中金16</t>
+          <t>26云产GTY1</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7028,58 +7202,58 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>246301.SH</t>
+          <t>520560.SZ</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5+3</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>30.0</v>
+        <v>5.0</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.15 ~ 2.05</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>21中金G8</t>
+          <t>23云产01</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>5.11Y</t>
+          <t>52D</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.6049</t>
+          <t>1.4346</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4300</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司</t>
+          <t>广州白云产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>B- 44.41</t>
+          <t>B- 36.62</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7106,60 +7280,68 @@
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X32" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>1.55%~1.65%</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z32" s="3"/>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过人民币60亿元(含60亿元),本期债券募集资金扣除发行费用后,拟全部用于补充流动资金,未来可能调整部分流动资金用于偿还有息债务</t>
+          <t>本期债券募集资金扣除发行费用后，拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司2026年面向专业投资者公开发行公司债券(第八期)(品种二)</t>
+          <t>广州白云产业投资集团有限公司2026年面向专业投资者非公开发行可续期低碳转型挂钩公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2034-11-02</t>
+          <t>2029-11-02</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
@@ -7180,37 +7362,37 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
         <is>
-          <t>2031-11-02</t>
+          <t/>
         </is>
       </c>
       <c r="AV32" s="3" t="inlineStr">
@@ -7220,7 +7402,7 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
@@ -7238,7 +7420,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26振兴K2</t>
+          <t>26金控Y1</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7248,12 +7430,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>246339.SH</t>
+          <t>520559.SZ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
@@ -7262,29 +7444,29 @@
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>2.30 ~ 3.30</t>
         </is>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26川振兴K1</t>
+          <t>25金控Y2</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2.63Y</t>
+          <t>1.44Y+N</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.6154</t>
+          <t>2.4308</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -7294,12 +7476,12 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>四川产业振兴基金投资集团有限公司</t>
+          <t>西安高新金融控股集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.95</t>
+          <t>B- 36.16</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7319,17 +7501,21 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X33" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>2.98%~3.08%</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -7338,17 +7524,17 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还有息负债及置换发行人基金前期出资。[23四川振兴MTN002(科创票据)]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,5亿元用于股权投资。</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司</t>
+          <t>中信建投证券股份有限公司,开源证券股份有限公司,西部证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7364,22 +7550,22 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>四川产业振兴基金投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)</t>
+          <t>西安高新金融控股集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2029-10-30</t>
+          <t>2029-11-02</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
@@ -7395,7 +7581,7 @@
       </c>
       <c r="AN33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="AO33" s="3" t="inlineStr">
@@ -7403,7 +7589,11 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP33" s="3"/>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
           <t>非银</t>
@@ -7411,12 +7601,12 @@
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
@@ -7436,7 +7626,7 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7729,7 +7919,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7500</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -7877,7 +8067,9 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ35" s="3"/>
+      <c r="AZ35" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
@@ -7913,14 +8105,22 @@
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>24鞍钢集K4</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>2.98Y</t>
+        </is>
+      </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5642</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -7961,7 +8161,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X36" s="3"/>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>1.80%~1.90%</t>
+        </is>
+      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8177,7 +8381,11 @@
           <t>8+</t>
         </is>
       </c>
-      <c r="X37" s="3"/>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>2.36%~2.46%</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -8361,7 +8569,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8300/1.6000</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -8401,7 +8609,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="X38" s="3"/>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>1.84%~1.94%</t>
+        </is>
+      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -8629,7 +8841,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X39" s="3"/>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -8849,7 +9065,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X40" s="3"/>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -9025,7 +9245,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/1.5150</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -9249,7 +9469,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6700/1.6700</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -9289,7 +9509,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X42" s="3"/>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -9426,7 +9650,11 @@
           <t>10-29 17:00</t>
         </is>
       </c>
-      <c r="C43" s="3"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>102684345.IB</t>
+        </is>
+      </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -9465,7 +9693,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6500/1.5700</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -9505,7 +9733,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X43" s="3"/>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>1.60%~1.70%</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -9642,7 +9874,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C44" s="3"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>102684353.IB</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -9681,7 +9917,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9700</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -9721,7 +9957,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X44" s="3"/>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>1.88%~1.98%</t>
+        </is>
+      </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -9845,7 +10085,9 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ44" s="3"/>
+      <c r="AZ44" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
@@ -9858,7 +10100,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C45" s="3"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>102684356.IB</t>
+        </is>
+      </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
           <t>1+1</t>
@@ -9937,7 +10183,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X45" s="3"/>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>1.48%~1.52%</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -10074,7 +10324,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C46" s="3"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>012682564.IB</t>
+        </is>
+      </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
           <t>0.49Y</t>
@@ -10153,7 +10407,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X46" s="3"/>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>3.08%~3.12%</t>
+        </is>
+      </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -10518,7 +10776,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C48" s="3"/>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>102684355.IB</t>
+        </is>
+      </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -10557,7 +10819,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8500/1.7500</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -10597,7 +10859,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X48" s="3"/>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -10734,7 +11000,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C49" s="3"/>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>102684351.IB</t>
+        </is>
+      </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
           <t>3+N</t>
@@ -10813,7 +11083,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X49" s="3"/>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>1.76%~1.86%</t>
+        </is>
+      </c>
       <c r="Y49" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -10950,7 +11224,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C50" s="3"/>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>102684350.IB</t>
+        </is>
+      </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -10989,7 +11267,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
@@ -11029,7 +11307,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X50" s="3"/>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.73%</t>
+        </is>
+      </c>
       <c r="Y50" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -11153,7 +11435,9 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ50" s="3"/>
+      <c r="AZ50" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
@@ -11166,7 +11450,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C51" s="3"/>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>042680361.IB</t>
+        </is>
+      </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
           <t>1Y</t>
@@ -11205,7 +11493,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4500/1.4000</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
@@ -11245,7 +11533,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X51" s="3"/>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>1.41%~1.45%</t>
+        </is>
+      </c>
       <c r="Y51" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -11382,7 +11674,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C52" s="3"/>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>042680362.IB</t>
+        </is>
+      </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
           <t>1Y</t>
@@ -11421,7 +11717,7 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5900</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
@@ -11457,7 +11753,11 @@
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>1.82%~1.86%</t>
+        </is>
+      </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -11598,7 +11898,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C53" s="3"/>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>102684339.IB</t>
+        </is>
+      </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -11637,7 +11941,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0800/--</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
@@ -11677,7 +11981,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X53" s="3"/>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>2.32%~2.42%</t>
+        </is>
+      </c>
       <c r="Y53" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -11801,7 +12109,9 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ53" s="3"/>
+      <c r="AZ53" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
@@ -11814,7 +12124,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C54" s="3"/>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>012682569.IB</t>
+        </is>
+      </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -11853,7 +12167,7 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9400</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
@@ -11893,7 +12207,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X54" s="3"/>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>1.87%~1.91%</t>
+        </is>
+      </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -12030,7 +12348,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C55" s="3"/>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>102684335.IB</t>
+        </is>
+      </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
           <t>2+1</t>
@@ -12069,7 +12391,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.1000</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
@@ -12109,7 +12431,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X55" s="3"/>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>2.11%~2.21%</t>
+        </is>
+      </c>
       <c r="Y55" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -12241,7 +12567,9 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ55" s="3"/>
+      <c r="AZ55" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
@@ -12254,7 +12582,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C56" s="3"/>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>102684343.IB</t>
+        </is>
+      </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
           <t>1+1</t>
@@ -12333,7 +12665,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X56" s="3"/>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>1.48%~1.52%</t>
+        </is>
+      </c>
       <c r="Y56" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -12470,7 +12806,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C57" s="3"/>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>102684333.IB</t>
+        </is>
+      </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -12549,7 +12889,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X57" s="3"/>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>1.65%~1.75%</t>
+        </is>
+      </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -12686,7 +13030,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C58" s="3"/>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>102690097.IB</t>
+        </is>
+      </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -12725,7 +13073,7 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
@@ -12765,7 +13113,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X58" s="3"/>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>1.59%~1.69%</t>
+        </is>
+      </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -12933,7 +13285,7 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
@@ -12973,7 +13325,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X59" s="3"/>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>1.62%~1.72%</t>
+        </is>
+      </c>
       <c r="Y59" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13153,7 +13509,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5900</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
@@ -13193,7 +13549,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X60" s="3"/>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>1.57%~1.67%</t>
+        </is>
+      </c>
       <c r="Y60" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13373,7 +13733,7 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9000/1.8600</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
@@ -13413,7 +13773,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X61" s="3"/>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y61" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13633,7 +13997,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X62" s="3"/>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>2.23%~2.33%</t>
+        </is>
+      </c>
       <c r="Y62" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13817,7 +14185,7 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6200/--</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
@@ -13857,7 +14225,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X63" s="3"/>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>1.58%~1.68%</t>
+        </is>
+      </c>
       <c r="Y63" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13994,7 +14366,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C64" s="3"/>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>102684334.IB</t>
+        </is>
+      </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -14073,7 +14449,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X64" s="3"/>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>1.73%~1.83%</t>
+        </is>
+      </c>
       <c r="Y64" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -14197,7 +14577,9 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ64" s="3"/>
+      <c r="AZ64" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
@@ -14253,7 +14635,7 @@
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7200</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
@@ -14293,7 +14675,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X65" s="3"/>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>1.89%~1.99%</t>
+        </is>
+      </c>
       <c r="Y65" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -14683,7 +15069,7 @@
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9700/1.8500</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
@@ -14723,7 +15109,11 @@
           <t>7-</t>
         </is>
       </c>
-      <c r="X67" s="3"/>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>2.66%~2.76%</t>
+        </is>
+      </c>
       <c r="Y67" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -14911,7 +15301,7 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6900</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
@@ -14951,7 +15341,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X68" s="3"/>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
       <c r="Y68" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -15175,7 +15569,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X69" s="3"/>
+      <c r="X69" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y69" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -15395,7 +15793,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X70" s="3"/>
+      <c r="X70" s="3" t="inlineStr">
+        <is>
+          <t>1.73%~1.83%</t>
+        </is>
+      </c>
       <c r="Y70" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -15532,7 +15934,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C71" s="3"/>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>102690091.IB</t>
+        </is>
+      </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -15599,9 +16005,17 @@
       <c r="U71" s="3"/>
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
-      <c r="X71" s="3"/>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.60%</t>
+        </is>
+      </c>
       <c r="Y71" s="3"/>
-      <c r="Z71" s="3"/>
+      <c r="Z71" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA71" s="3" t="inlineStr">
         <is>
           <t>香港特别行政区-九龙区</t>
@@ -15775,7 +16189,7 @@
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5750/1.5500</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
@@ -15815,7 +16229,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X72" s="3"/>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>1.62%~1.72%</t>
+        </is>
+      </c>
       <c r="Y72" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -15956,7 +16374,11 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C73" s="3"/>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>032680610.IB</t>
+        </is>
+      </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -15995,7 +16417,7 @@
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9400</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
@@ -16035,7 +16457,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X73" s="3"/>
+      <c r="X73" s="3" t="inlineStr">
+        <is>
+          <t>1.84%~1.94%</t>
+        </is>
+      </c>
       <c r="Y73" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -16163,7 +16589,9 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ73" s="3"/>
+      <c r="AZ73" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
@@ -16219,7 +16647,7 @@
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5700/1.5400</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
@@ -16259,7 +16687,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X74" s="3"/>
+      <c r="X74" s="3" t="inlineStr">
+        <is>
+          <t>1.53%~1.63%</t>
+        </is>
+      </c>
       <c r="Y74" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -16388,7 +16820,7 @@
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>26金控Y1</t>
+          <t>26京住总MTN003B</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -16398,58 +16830,58 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>520559.SZ</t>
+          <t>102684336.IB</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 3.30</t>
+          <t>1.78 ~ 2.58</t>
         </is>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>25金控Y2</t>
+          <t>26京住总MTN002B</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>1.44Y+N</t>
+          <t>2.36Y</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>2.4308</t>
+          <t>2.0894</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0000</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>西安高新金融控股集团有限公司</t>
+          <t>北京住总房地产开发有限责任公司</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>B- 36.16</t>
+          <t>C- 22.09</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -16459,7 +16891,7 @@
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>10-29 16:00</t>
+          <t>10-29 09:00</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr">
@@ -16469,42 +16901,54 @@
       </c>
       <c r="T75" s="3" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="U75" s="3"/>
       <c r="V75" s="3"/>
       <c r="W75" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X75" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X75" s="3" t="inlineStr">
+        <is>
+          <t>2.24%~2.34%</t>
+        </is>
+      </c>
       <c r="Y75" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z75" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z75" s="3"/>
       <c r="AA75" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB75" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还公司有息债务,5亿元用于股权投资。</t>
+          <t>募集资金用于偿还到期的23京住总MTN003本金【23京住总MTN003】</t>
         </is>
       </c>
       <c r="AC75" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,开源证券股份有限公司,西部证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD75" s="3"/>
+          <t>北京银行股份有限公司,上海银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD75" s="3" t="inlineStr">
+        <is>
+          <t>北京住总集团有限责任公司</t>
+        </is>
+      </c>
       <c r="AE75" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF75" s="3" t="inlineStr">
@@ -16514,83 +16958,83 @@
       </c>
       <c r="AG75" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH75" s="3" t="inlineStr">
         <is>
-          <t>西安高新金融控股集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
+          <t>北京住总房地产开发有限责任公司2026年度第三期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI75" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ75" s="3" t="inlineStr">
         <is>
-          <t>2029-11-02</t>
+          <t>2029-10-30</t>
         </is>
       </c>
       <c r="AK75" s="3"/>
       <c r="AL75" s="3" t="inlineStr">
         <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="AM75" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AN75" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AO75" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP75" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ75" s="3" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+      <c r="AR75" s="3" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AS75" s="3" t="inlineStr">
+        <is>
+          <t>住宅楼房</t>
+        </is>
+      </c>
+      <c r="AT75" s="3" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AU75" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM75" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AN75" s="3" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="AO75" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP75" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ75" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR75" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AS75" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AT75" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU75" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV75" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW75" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX75" s="3" t="inlineStr">
@@ -16603,12 +17047,14 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="AZ75" s="3"/>
+      <c r="AZ75" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="76" customHeight="true" ht="18.0">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>26京住总MTN003B</t>
+          <t>26九州通MTN003(支持养老产业)</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -16616,10 +17062,14 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C76" s="3"/>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>102684346.IB</t>
+        </is>
+      </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
@@ -16628,19 +17078,19 @@
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>1.78 ~ 2.58</t>
+          <t>1.70 ~ 2.05</t>
         </is>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>26京住总MTN002B</t>
+          <t>26九州通MTN002(科创债)</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
@@ -16650,22 +17100,22 @@
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>2.0894</t>
+          <t>1.9536</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9800</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>北京住总房地产开发有限责任公司</t>
+          <t>九州通医药集团股份有限公司</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>C- 22.09</t>
+          <t>C- 22.93</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -16695,37 +17145,33 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X76" s="3"/>
+      <c r="X76" s="3" t="inlineStr">
+        <is>
+          <t>1.78%~1.88%</t>
+        </is>
+      </c>
       <c r="Y76" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z76" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z76" s="3"/>
       <c r="AA76" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB76" s="3" t="inlineStr">
         <is>
-          <t>募集资金用于偿还到期的23京住总MTN003本金【23京住总MTN003】</t>
+          <t>本期中期票据发行金额5亿元,其中:2.5亿元拟用于老年群体药品采购,剩余募集资金拟用于补充发行人运营流动资金。</t>
         </is>
       </c>
       <c r="AC76" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司,上海银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD76" s="3" t="inlineStr">
-        <is>
-          <t>北京住总集团有限责任公司</t>
-        </is>
-      </c>
+          <t>招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD76" s="3"/>
       <c r="AE76" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -16733,7 +17179,7 @@
       </c>
       <c r="AF76" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG76" s="3" t="inlineStr">
@@ -16743,7 +17189,7 @@
       </c>
       <c r="AH76" s="3" t="inlineStr">
         <is>
-          <t>北京住总房地产开发有限责任公司2026年度第三期中期票据(品种二)</t>
+          <t>九州通医药集团股份有限公司2026年度第三期中期票据(支持养老产业)</t>
         </is>
       </c>
       <c r="AI76" s="3" t="inlineStr">
@@ -16753,7 +17199,7 @@
       </c>
       <c r="AJ76" s="3" t="inlineStr">
         <is>
-          <t>2029-10-30</t>
+          <t>2031-10-30</t>
         </is>
       </c>
       <c r="AK76" s="3"/>
@@ -16779,27 +17225,27 @@
       </c>
       <c r="AP76" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ76" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR76" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>医药流通</t>
         </is>
       </c>
       <c r="AS76" s="3" t="inlineStr">
         <is>
-          <t>住宅楼房</t>
+          <t>医药流通</t>
         </is>
       </c>
       <c r="AT76" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>医药商业</t>
         </is>
       </c>
       <c r="AU76" s="3" t="inlineStr">
@@ -16809,7 +17255,7 @@
       </c>
       <c r="AV76" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW76" s="3" t="inlineStr">
@@ -16832,7 +17278,7 @@
     <row r="77" customHeight="true" ht="18.0">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>26九州通MTN003(支持养老产业)</t>
+          <t>26桂投资MTN003B</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -16840,41 +17286,45 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C77" s="3"/>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>102684352.IB</t>
+        </is>
+      </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.05</t>
+          <t>1.85 ~ 2.35</t>
         </is>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>26九州通MTN002(科创债)</t>
+          <t>26桂投资MTN002</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>2.36Y</t>
+          <t>4.97Y+N</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>1.9536</t>
+          <t>2.1416</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -16884,12 +17334,12 @@
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>九州通医药集团股份有限公司</t>
+          <t>广西投资集团有限公司</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>C- 22.93</t>
+          <t>C- 18.06</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -16916,10 +17366,14 @@
       <c r="V77" s="3"/>
       <c r="W77" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X77" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X77" s="3" t="inlineStr">
+        <is>
+          <t>1.95%~2.05%</t>
+        </is>
+      </c>
       <c r="Y77" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -16928,17 +17382,17 @@
       <c r="Z77" s="3"/>
       <c r="AA77" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB77" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额5亿元,其中:2.5亿元拟用于老年群体药品采购,剩余募集资金拟用于补充发行人运营流动资金。</t>
+          <t>发行人本次中期票据发行金额不超过5亿元，募集资金全部用于发行人本部到期的债务融资工具[24桂投资MTN009]</t>
         </is>
       </c>
       <c r="AC77" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>中信银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD77" s="3"/>
@@ -16949,7 +17403,7 @@
       </c>
       <c r="AF77" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG77" s="3" t="inlineStr">
@@ -16959,7 +17413,7 @@
       </c>
       <c r="AH77" s="3" t="inlineStr">
         <is>
-          <t>九州通医药集团股份有限公司2026年度第三期中期票据(支持养老产业)</t>
+          <t>广西投资集团有限公司2026年度第三期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI77" s="3" t="inlineStr">
@@ -16995,27 +17449,27 @@
       </c>
       <c r="AP77" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ77" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR77" s="3" t="inlineStr">
         <is>
-          <t>医药流通</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS77" s="3" t="inlineStr">
         <is>
-          <t>医药流通</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT77" s="3" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>工业金属</t>
         </is>
       </c>
       <c r="AU77" s="3" t="inlineStr">
@@ -17030,12 +17484,12 @@
       </c>
       <c r="AW77" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX77" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY77" s="3" t="inlineStr">
@@ -17048,7 +17502,7 @@
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>26桂投资MTN003B</t>
+          <t>26豫国01</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -17056,41 +17510,45 @@
           <t>10-29 18:00</t>
         </is>
       </c>
-      <c r="C78" s="3"/>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>284381.SH</t>
+        </is>
+      </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>1.85 ~ 2.35</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>25桂投资MTN005</t>
+          <t>24豫国K1</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>3.58Y</t>
+          <t>2.78Y</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>1.7891</t>
+          <t>1.6951</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -17100,12 +17558,12 @@
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>广西投资集团有限公司</t>
+          <t>河南国有资本运营集团有限公司</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>C- 18.06</t>
+          <t>B- 48.25</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -17115,7 +17573,7 @@
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>10-29 09:00</t>
+          <t>10-29 16:00</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr">
@@ -17125,17 +17583,21 @@
       </c>
       <c r="T78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="U78" s="3"/>
       <c r="V78" s="3"/>
       <c r="W78" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X78" s="3"/>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X78" s="3" t="inlineStr">
+        <is>
+          <t>1.81%~1.91%</t>
+        </is>
+      </c>
       <c r="Y78" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -17144,23 +17606,23 @@
       <c r="Z78" s="3"/>
       <c r="AA78" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB78" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行金额不超过5亿元，募集资金全部用于发行人本部到期的债务融资工具[24桂投资MTN009]</t>
+          <t>本期债券发行规模为不超过15亿元(含15亿元),本期债券募集资金扣除发行费用后,12亿元用于偿还有息负债本金,3亿元用于偿还到期的公司债券本金。[23豫国01]</t>
         </is>
       </c>
       <c r="AC78" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中原证券股份有限公司,华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD78" s="3"/>
       <c r="AE78" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF78" s="3" t="inlineStr">
@@ -17170,40 +17632,44 @@
       </c>
       <c r="AG78" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH78" s="3" t="inlineStr">
         <is>
-          <t>广西投资集团有限公司2026年度第三期中期票据(品种二)</t>
+          <t>河南国有资本运营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI78" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ78" s="3" t="inlineStr">
         <is>
-          <t>2031-10-30</t>
-        </is>
-      </c>
-      <c r="AK78" s="3"/>
+          <t>2031-11-02</t>
+        </is>
+      </c>
+      <c r="AK78" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL78" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM78" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AN78" s="3" t="inlineStr">
+        <is>
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="AM78" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AN78" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
       <c r="AO78" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -17211,7 +17677,7 @@
       </c>
       <c r="AP78" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ78" s="3" t="inlineStr">
@@ -17231,7 +17697,7 @@
       </c>
       <c r="AT78" s="3" t="inlineStr">
         <is>
-          <t>工业金属</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AU78" s="3" t="inlineStr">
@@ -17246,12 +17712,12 @@
       </c>
       <c r="AW78" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX78" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY78" s="3" t="inlineStr">
@@ -17264,68 +17730,68 @@
     <row r="79" customHeight="true" ht="18.0">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>26豫国01</t>
+          <t>26浦发银行债02</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>10-29 18:00</t>
+          <t>10-29 16:30</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>284381.SH</t>
+          <t>212680091.IB</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H79" s="3"/>
+        <v>50.0</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="G79" s="3"/>
+      <c r="H79" s="4" t="n">
+        <v>1.49</v>
+      </c>
       <c r="I79" s="3"/>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>24豫国K1</t>
+          <t>26浦发银行债01</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>2.78Y</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>1.6951</t>
+          <t>1.4824</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4850/1.4800</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>河南国有资本运营集团有限公司</t>
+          <t>上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>B- 48.25</t>
+          <t>A+ 84.30</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -17335,7 +17801,7 @@
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>10-29 16:00</t>
+          <t>10-29 09:30</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr">
@@ -17345,17 +17811,21 @@
       </c>
       <c r="T79" s="3" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="U79" s="3"/>
       <c r="V79" s="3"/>
       <c r="W79" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X79" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X79" s="3" t="inlineStr">
+        <is>
+          <t>1.49%~1.59%</t>
+        </is>
+      </c>
       <c r="Y79" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -17364,23 +17834,19 @@
       <c r="Z79" s="3"/>
       <c r="AA79" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB79" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过15亿元(含15亿元),本期债券募集资金扣除发行费用后,12亿元用于偿还有息负债本金,3亿元用于偿还到期的公司债券本金。[23豫国01]</t>
-        </is>
-      </c>
-      <c r="AC79" s="3" t="inlineStr">
-        <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中原证券股份有限公司,华泰联合证券有限责任公司</t>
-        </is>
-      </c>
+          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC79" s="3"/>
       <c r="AD79" s="3"/>
       <c r="AE79" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF79" s="3" t="inlineStr">
@@ -17390,29 +17856,25 @@
       </c>
       <c r="AG79" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH79" s="3" t="inlineStr">
         <is>
-          <t>河南国有资本运营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>上海浦东发展银行股份有限公司2026年第二期金融债券</t>
         </is>
       </c>
       <c r="AI79" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ79" s="3" t="inlineStr">
         <is>
-          <t>2031-11-02</t>
-        </is>
-      </c>
-      <c r="AK79" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-30</t>
+        </is>
+      </c>
+      <c r="AK79" s="3"/>
       <c r="AL79" s="3" t="inlineStr">
         <is>
           <t/>
@@ -17425,37 +17887,37 @@
       </c>
       <c r="AN79" s="3" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AO79" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP79" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ79" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR79" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS79" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT79" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU79" s="3" t="inlineStr">
